--- a/tame_output/MOZAIC/data/universe_last2023-07-30.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-30.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>570.4646515422235</v>
+        <v>569.3799380152742</v>
       </c>
       <c r="E2" t="n">
-        <v>6448.112503738233</v>
+        <v>5914.215678152056</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6184070658209821</v>
+        <v>0.6146686277241993</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4968229309781526</v>
+        <v>0.4968374838121571</v>
       </c>
       <c r="H2" t="n">
-        <v>1.244723275158522</v>
+        <v>1.237162347349363</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>227.3466420119571</v>
+        <v>226.8320436558287</v>
       </c>
       <c r="E3" t="n">
-        <v>2498.260093862026</v>
+        <v>2570.229831277502</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2703635241447606</v>
+        <v>0.2661210228365194</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5956376679198784</v>
+        <v>0.5956531534853011</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4539060215733843</v>
+        <v>0.4467717853576115</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907000850976625</v>
+        <v>0.8907077253157719</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067854336874275</v>
+        <v>1.067859979780931</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.4276439270318</v>
+        <v>38.2383222345975</v>
       </c>
       <c r="E4" t="n">
-        <v>732.4397403479019</v>
+        <v>846.5506132624161</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7692112276613214</v>
+        <v>0.8165187291142624</v>
       </c>
       <c r="G4" t="n">
-        <v>1.104470948457489</v>
+        <v>1.104565806591361</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6964522052260465</v>
+        <v>0.7392214427078827</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4736008048056128</v>
+        <v>0.4733780693739588</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052846592736854</v>
+        <v>1.052410991636042</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.30927128367718</v>
+        <v>37.27728684090253</v>
       </c>
       <c r="E5" t="n">
-        <v>326.2082659594413</v>
+        <v>375.4026812245631</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3272516252129735</v>
+        <v>-0.327996379006498</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5593908163022528</v>
+        <v>0.5593903554474049</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5850142971173685</v>
+        <v>-0.5863461459648582</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7362243891899705</v>
+        <v>0.7362139702231547</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8289415330322488</v>
+        <v>0.8289048389194793</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.20956566640797</v>
+        <v>11.22251350521524</v>
       </c>
       <c r="E6" t="n">
-        <v>477.7560336903666</v>
+        <v>494.6629190652158</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4625291961937036</v>
+        <v>-0.4616259875694019</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8125507291016313</v>
+        <v>0.8125444524706429</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5692311625947134</v>
+        <v>-0.5681239791444892</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6667634955514794</v>
+        <v>0.6667535843088065</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090487436604514</v>
+        <v>1.0904308627001</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.97275103153823</v>
+        <v>11.05226207802491</v>
       </c>
       <c r="E7" t="n">
-        <v>152.3054396741389</v>
+        <v>151.7771890369737</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2907815497200198</v>
+        <v>-0.2859263119170335</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7118679306033032</v>
+        <v>0.7119220428049979</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4084768216396325</v>
+        <v>-0.4016258729543951</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7507698539427954</v>
+        <v>0.7505934143093449</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075733322601214</v>
+        <v>1.075530760543658</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.16623470449158</v>
+        <v>10.09416135784227</v>
       </c>
       <c r="E8" t="n">
-        <v>260.2333373452744</v>
+        <v>246.4445776658258</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.293230747412473</v>
+        <v>-0.3007655909552989</v>
       </c>
       <c r="G8" t="n">
-        <v>1.167337714152731</v>
+        <v>1.167393396376064</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2511961567397004</v>
+        <v>-0.2576385920024601</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7374342517318981</v>
+        <v>0.7374593117762522</v>
       </c>
       <c r="N8" t="n">
-        <v>1.73267931103707</v>
+        <v>1.732770088234973</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.485732866330415</v>
+        <v>7.359375323843868</v>
       </c>
       <c r="E9" t="n">
-        <v>177.1467466883655</v>
+        <v>184.6621368223872</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4516749260643356</v>
+        <v>0.4184116742665642</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4798268385454295</v>
+        <v>0.480137725558456</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9413290165959974</v>
+        <v>0.8714409470322351</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6764002036276034</v>
+        <v>0.6763077416045171</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6532608522298455</v>
+        <v>0.653575608547157</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.964228708134634</v>
+        <v>6.948356878402173</v>
       </c>
       <c r="E10" t="n">
-        <v>491.1874194901928</v>
+        <v>586.1638876259005</v>
       </c>
       <c r="F10" t="n">
-        <v>1.077552368651978</v>
+        <v>1.070501931056221</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8190451918003077</v>
+        <v>0.8190387993470455</v>
       </c>
       <c r="H10" t="n">
-        <v>1.315620162891692</v>
+        <v>1.307022245966426</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6637021466204805</v>
+        <v>0.6637054584923396</v>
       </c>
       <c r="N10" t="n">
-        <v>1.094156525558905</v>
+        <v>1.094121396945905</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.696145116989055</v>
+        <v>6.631729296491348</v>
       </c>
       <c r="E11" t="n">
-        <v>193.6701423023798</v>
+        <v>194.6927067830577</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.26438082637742</v>
+        <v>-0.2737145787050274</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9550111361315583</v>
+        <v>0.9550873259218629</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2768353335107079</v>
+        <v>-0.2865859186654314</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7132948878917796</v>
+        <v>0.7133287780765154</v>
       </c>
       <c r="N11" t="n">
-        <v>1.371121417325071</v>
+        <v>1.371255787564107</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.350243840697658</v>
+        <v>6.324059329028994</v>
       </c>
       <c r="E12" t="n">
-        <v>69.8455030307934</v>
+        <v>74.59233173802028</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.267205426559966</v>
+        <v>-0.2726310725579797</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6559889578294016</v>
+        <v>0.6560105103238145</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4073322018165072</v>
+        <v>-0.4155894886857922</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7887939535779093</v>
+        <v>0.7888296805309443</v>
       </c>
       <c r="N12" t="n">
-        <v>1.04149806960593</v>
+        <v>1.041548953418587</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.719718205628721</v>
+        <v>4.732328734080903</v>
       </c>
       <c r="E13" t="n">
-        <v>129.7121294349535</v>
+        <v>147.1237509723308</v>
       </c>
       <c r="F13" t="n">
-        <v>1.719929795754973</v>
+        <v>1.724447961381451</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8579421723204959</v>
+        <v>0.857941040877322</v>
       </c>
       <c r="H13" t="n">
-        <v>2.004715295790903</v>
+        <v>2.009984228774099</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6033761898316657</v>
+        <v>0.6033502406910402</v>
       </c>
       <c r="N13" t="n">
-        <v>1.041944416718976</v>
+        <v>1.041867714046634</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.583398016129614</v>
+        <v>4.578100277300508</v>
       </c>
       <c r="E14" t="n">
-        <v>55.7785972941405</v>
+        <v>58.97804019276096</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3960869088382117</v>
+        <v>-0.3966989129358959</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8471449056425666</v>
+        <v>0.8471439846861829</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4675550855585638</v>
+        <v>-0.4682780260581671</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601751496519039</v>
+        <v>0.7601570354796823</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296193201380241</v>
+        <v>1.296122939602846</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.324765191927963</v>
+        <v>4.38987147368974</v>
       </c>
       <c r="E15" t="n">
-        <v>117.3105086644669</v>
+        <v>139.9760464243933</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6056889342212699</v>
+        <v>0.6233974175372166</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9572403052790782</v>
+        <v>0.9572671416675911</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6327449135613701</v>
+        <v>0.6512261733451308</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5137951031520314</v>
+        <v>0.5136817810410373</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9899409844546276</v>
+        <v>0.9897214004283607</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.210601508345412</v>
+        <v>4.173431482358167</v>
       </c>
       <c r="E16" t="n">
-        <v>132.1229642810331</v>
+        <v>130.6647178604804</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.003926246020302893</v>
+        <v>-0.01687187236745102</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7914147617184305</v>
+        <v>0.7915237634594861</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.004961047241243867</v>
+        <v>-0.02131568645988556</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7136309318871119</v>
+        <v>0.713654255772887</v>
       </c>
       <c r="N16" t="n">
-        <v>1.136779360812507</v>
+        <v>1.136939785629782</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.644080087780682</v>
+        <v>3.692199700519849</v>
       </c>
       <c r="E17" t="n">
-        <v>89.96798563861655</v>
+        <v>110.9045280414452</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1219733218632004</v>
+        <v>-0.108330675084786</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7532377697392242</v>
+        <v>0.7533266978301731</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1619320309779851</v>
+        <v>-0.1438030477305712</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7215925933683323</v>
+        <v>0.7213299936563626</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094013101647691</v>
+        <v>1.09371204845014</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.148369394578045</v>
+        <v>3.130776454754783</v>
       </c>
       <c r="E18" t="n">
-        <v>43.07101011891726</v>
+        <v>43.69096516994713</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4563698598465815</v>
+        <v>-0.4625390530954598</v>
       </c>
       <c r="G18" t="n">
-        <v>0.743196060219066</v>
+        <v>0.743221368888348</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6140638847198153</v>
+        <v>-0.6223435876006759</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7644024172612808</v>
+        <v>0.7644608571685078</v>
       </c>
       <c r="N18" t="n">
-        <v>1.14346748007792</v>
+        <v>1.143560345662542</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.989697651822547</v>
+        <v>2.973414334091433</v>
       </c>
       <c r="E19" t="n">
-        <v>70.07293806242284</v>
+        <v>55.39558176545053</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1238514608227019</v>
+        <v>0.1164649691029389</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4794868650952027</v>
+        <v>0.4795204651299567</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2583000074425627</v>
+        <v>0.2428779949389132</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7177462202686552</v>
+        <v>0.7177851359439592</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6927012897995284</v>
+        <v>0.6927670988313513</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.648019396284733</v>
+        <v>2.629836468879698</v>
       </c>
       <c r="E20" t="n">
-        <v>75.35783543926118</v>
+        <v>73.79124709733067</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.298480592198991</v>
+        <v>-0.3050451860124402</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7755214364481802</v>
+        <v>0.7755548219301212</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3848772943866076</v>
+        <v>-0.3933251104715913</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7325390200845852</v>
+        <v>0.7325787556725553</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143465161706317</v>
+        <v>1.143542918795202</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-30.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-30.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>569.3799380152742</v>
+        <v>569.0401723582995</v>
       </c>
       <c r="E2" t="n">
-        <v>5914.215678152056</v>
+        <v>5985.328339902592</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6146686277241993</v>
+        <v>0.6130794786684091</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4968374838121571</v>
+        <v>0.4968460629465444</v>
       </c>
       <c r="H2" t="n">
-        <v>1.237162347349363</v>
+        <v>1.233942511353602</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>226.8320436558287</v>
+        <v>226.7268614363142</v>
       </c>
       <c r="E3" t="n">
-        <v>2570.229831277502</v>
+        <v>2596.281367508645</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2661210228365194</v>
+        <v>0.2653689910765051</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5956531534853011</v>
+        <v>0.5956573366572696</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4467717853576115</v>
+        <v>0.44550612364772</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907077253157719</v>
+        <v>0.8907087361553446</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067859979780931</v>
+        <v>1.06785025198587</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.2383222345975</v>
+        <v>37.9571148125732</v>
       </c>
       <c r="E4" t="n">
-        <v>846.5506132624161</v>
+        <v>929.8342684016194</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8165187291142624</v>
+        <v>0.7966847047166119</v>
       </c>
       <c r="G4" t="n">
-        <v>1.104565806591361</v>
+        <v>1.10446895115448</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7392214427078827</v>
+        <v>0.721328294366132</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4733780693739588</v>
+        <v>0.4734821343699042</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052410991636042</v>
+        <v>1.052531871212948</v>
       </c>
     </row>
     <row r="5">
@@ -675,10 +675,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.27728684090253</v>
+        <v>37.30033358176787</v>
       </c>
       <c r="E5" t="n">
-        <v>375.4026812245631</v>
+        <v>378.9139911043348</v>
       </c>
       <c r="F5" t="n">
         <v>-0.327996379006498</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7362139702231547</v>
+        <v>0.7362018728339332</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8289048389194793</v>
+        <v>0.8288769058232972</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.22251350521524</v>
+        <v>11.21681275604477</v>
       </c>
       <c r="E6" t="n">
-        <v>494.6629190652158</v>
+        <v>500.943964991162</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4616259875694019</v>
+        <v>-0.463341753449264</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8125444524706429</v>
+        <v>0.812558541603519</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5681239791444892</v>
+        <v>-0.5702256880284542</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6667535843088065</v>
+        <v>0.6667734409266665</v>
       </c>
       <c r="N6" t="n">
-        <v>1.0904308627001</v>
+        <v>1.090463415421334</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.05226207802491</v>
+        <v>11.02740343787273</v>
       </c>
       <c r="E7" t="n">
-        <v>151.7771890369737</v>
+        <v>153.4963656940443</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2859263119170335</v>
+        <v>-0.2892651947487902</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7119220428049979</v>
+        <v>0.7118796223224992</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4016258729543951</v>
+        <v>-0.4063400407572642</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7505934143093449</v>
+        <v>0.7506652775131005</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075530760543658</v>
+        <v>1.075551069233559</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.09416135784227</v>
+        <v>10.09782745562311</v>
       </c>
       <c r="E8" t="n">
-        <v>246.4445776658258</v>
+        <v>247.4292765042955</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3007655909552989</v>
+        <v>-0.3022700873725092</v>
       </c>
       <c r="G8" t="n">
-        <v>1.167393396376064</v>
+        <v>1.167413122349056</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2576385920024601</v>
+        <v>-0.2589229824351164</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7374593117762522</v>
+        <v>0.7374683580992097</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732770088234973</v>
+        <v>1.732790702730913</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.359375323843868</v>
+        <v>7.36060542201128</v>
       </c>
       <c r="E9" t="n">
-        <v>184.6621368223872</v>
+        <v>186.3050406587133</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4184116742665642</v>
+        <v>0.417252185388594</v>
       </c>
       <c r="G9" t="n">
-        <v>0.480137725558456</v>
+        <v>0.4801633185249929</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8714409470322351</v>
+        <v>0.8689797185473169</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6763077416045171</v>
+        <v>0.676337423674767</v>
       </c>
       <c r="N9" t="n">
-        <v>0.653575608547157</v>
+        <v>0.6536278457524182</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.948356878402173</v>
+        <v>6.952366649239971</v>
       </c>
       <c r="E10" t="n">
-        <v>586.1638876259005</v>
+        <v>597.4403578615437</v>
       </c>
       <c r="F10" t="n">
-        <v>1.070501931056221</v>
+        <v>1.064631234710496</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8190387993470455</v>
+        <v>0.8190414646223692</v>
       </c>
       <c r="H10" t="n">
-        <v>1.307022245966426</v>
+        <v>1.299850228219348</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6637054584923396</v>
+        <v>0.6637240409748977</v>
       </c>
       <c r="N10" t="n">
-        <v>1.094121396945905</v>
+        <v>1.094136697795762</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.631729296491348</v>
+        <v>6.631409961288135</v>
       </c>
       <c r="E11" t="n">
-        <v>194.6927067830577</v>
+        <v>195.9815026282848</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2737145787050274</v>
+        <v>-0.2750846245505572</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9550873259218629</v>
+        <v>0.9551089985226601</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2865859186654314</v>
+        <v>-0.2880138549380767</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7133287780765154</v>
+        <v>0.7133402931249181</v>
       </c>
       <c r="N11" t="n">
-        <v>1.371255787564107</v>
+        <v>1.371285361368968</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.324059329028994</v>
+        <v>6.319146997577179</v>
       </c>
       <c r="E12" t="n">
-        <v>74.59233173802028</v>
+        <v>76.1146518267694</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2726310725579797</v>
+        <v>-0.2744996004135839</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6560105103238145</v>
+        <v>0.6560322263919859</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4155894886857922</v>
+        <v>-0.4184239574986482</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7888296805309443</v>
+        <v>0.7888407850640553</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041548953418587</v>
+        <v>1.04158010918978</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.732328734080903</v>
+        <v>4.728459316104344</v>
       </c>
       <c r="E13" t="n">
-        <v>147.1237509723308</v>
+        <v>148.6808055670004</v>
       </c>
       <c r="F13" t="n">
-        <v>1.724447961381451</v>
+        <v>1.722941693880423</v>
       </c>
       <c r="G13" t="n">
-        <v>0.857941040877322</v>
+        <v>0.857941154171362</v>
       </c>
       <c r="H13" t="n">
-        <v>2.009984228774099</v>
+        <v>2.008228286407962</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6033502406910402</v>
+        <v>0.6033457975642775</v>
       </c>
       <c r="N13" t="n">
-        <v>1.041867714046634</v>
+        <v>1.041842189222357</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.578100277300508</v>
+        <v>4.58829966462755</v>
       </c>
       <c r="E14" t="n">
-        <v>58.97804019276096</v>
+        <v>60.32526692037459</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3966989129358959</v>
+        <v>-0.3954747466752417</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8471439846861829</v>
+        <v>0.8471467191951157</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4682780260581671</v>
+        <v>-0.4668314681676239</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601570354796823</v>
+        <v>0.7601178715108391</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296122939602846</v>
+        <v>1.296037966434007</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.38987147368974</v>
+        <v>4.362660514720453</v>
       </c>
       <c r="E15" t="n">
-        <v>139.9760464243933</v>
+        <v>155.9630991544506</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6233974175372166</v>
+        <v>0.6152181223323197</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9572671416675911</v>
+        <v>0.9572431688649938</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6512261733451308</v>
+        <v>0.6426978455869115</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5136817810410373</v>
+        <v>0.5137228796511476</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9897214004283607</v>
+        <v>0.9897587077964273</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.173431482358167</v>
+        <v>4.174382532050514</v>
       </c>
       <c r="E16" t="n">
-        <v>130.6647178604804</v>
+        <v>132.6044112776335</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.01687187236745102</v>
+        <v>-0.01976168993488692</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7915237634594861</v>
+        <v>0.79156963644908</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.02131568645988556</v>
+        <v>-0.02496519450081022</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.713654255772887</v>
+        <v>0.713663848474843</v>
       </c>
       <c r="N16" t="n">
-        <v>1.136939785629782</v>
+        <v>1.137001327400801</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.692199700519849</v>
+        <v>3.697122049157884</v>
       </c>
       <c r="E17" t="n">
-        <v>110.9045280414452</v>
+        <v>113.6986572024783</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.108330675084786</v>
+        <v>-0.1030836896658011</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7533266978301731</v>
+        <v>0.7534229365038544</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1438030477305712</v>
+        <v>-0.1368204824559037</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7213299936563626</v>
+        <v>0.7211244881016805</v>
       </c>
       <c r="N17" t="n">
-        <v>1.09371204845014</v>
+        <v>1.093521253219353</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.130776454754783</v>
+        <v>3.130276284033723</v>
       </c>
       <c r="E18" t="n">
-        <v>43.69096516994713</v>
+        <v>44.07111596085822</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4625390530954598</v>
+        <v>-0.462859039986022</v>
       </c>
       <c r="G18" t="n">
-        <v>0.743221368888348</v>
+        <v>0.7432261850188765</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6223435876006759</v>
+        <v>-0.6227700924911119</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7644608571685078</v>
+        <v>0.7644657513648043</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143560345662542</v>
+        <v>1.143555330991084</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.973414334091433</v>
+        <v>2.972566338381673</v>
       </c>
       <c r="E19" t="n">
-        <v>55.39558176545053</v>
+        <v>52.50145548897815</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1164649691029389</v>
+        <v>0.1155425308376925</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4795204651299567</v>
+        <v>0.479529333982196</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2428779949389132</v>
+        <v>0.2409498703200968</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7177851359439592</v>
+        <v>0.7177957610405643</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6927670988313513</v>
+        <v>0.6927782041498399</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.629836468879698</v>
+        <v>2.628221986259251</v>
       </c>
       <c r="E20" t="n">
-        <v>73.79124709733067</v>
+        <v>75.32567388878741</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3050451860124402</v>
+        <v>-0.3070618933816294</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7755548219301212</v>
+        <v>0.7755818472602986</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3933251104715913</v>
+        <v>-0.3959116558314369</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7325787556725553</v>
+        <v>0.7325915878483626</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143542918795202</v>
+        <v>1.143583051903783</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-30.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-30.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>569.0401723582995</v>
+        <v>570.1762349451532</v>
       </c>
       <c r="E2" t="n">
-        <v>5985.328339902592</v>
+        <v>6050.688792153733</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6130794786684091</v>
+        <v>0.6178829152401264</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4968460629465444</v>
+        <v>0.4968244955197113</v>
       </c>
       <c r="H2" t="n">
-        <v>1.233942511353602</v>
+        <v>1.243664353936051</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>226.7268614363142</v>
+        <v>227.0418270726495</v>
       </c>
       <c r="E3" t="n">
-        <v>2596.281367508645</v>
+        <v>2598.917505811584</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2653689910765051</v>
+        <v>0.2678067121424503</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5956573366572696</v>
+        <v>0.5956453510446934</v>
       </c>
       <c r="H3" t="n">
-        <v>0.44550612364772</v>
+        <v>0.4496076594449167</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907087361553446</v>
+        <v>0.8907046091411581</v>
       </c>
       <c r="N3" t="n">
-        <v>1.06785025198587</v>
+        <v>1.067870172210465</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.9571148125732</v>
+        <v>37.95162301962845</v>
       </c>
       <c r="E4" t="n">
-        <v>929.8342684016194</v>
+        <v>957.7764646834712</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7966847047166119</v>
+        <v>0.8023939008828924</v>
       </c>
       <c r="G4" t="n">
-        <v>1.10446895115448</v>
+        <v>1.104488423127185</v>
       </c>
       <c r="H4" t="n">
-        <v>0.721328294366132</v>
+        <v>0.7264846639234481</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4734821343699042</v>
+        <v>0.4735095636840184</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052531871212948</v>
+        <v>1.052657097315472</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.30033358176787</v>
+        <v>37.27671227609543</v>
       </c>
       <c r="E5" t="n">
-        <v>378.9139911043348</v>
+        <v>378.3638336194885</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.327996379006498</v>
+        <v>-0.3276240283829599</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5593903554474049</v>
+        <v>0.5593903845380145</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5863461459648582</v>
+        <v>-0.5856804790335032</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7362018728339332</v>
+        <v>0.7362269145173652</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8288769058232972</v>
+        <v>0.8289411261582315</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.21681275604477</v>
+        <v>11.24806583385351</v>
       </c>
       <c r="E6" t="n">
-        <v>500.943964991162</v>
+        <v>497.9088632434308</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.463341753449264</v>
+        <v>-0.4607223926955714</v>
       </c>
       <c r="G6" t="n">
-        <v>0.812558541603519</v>
+        <v>0.8125407063448896</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5702256880284542</v>
+        <v>-0.5670145373615459</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6667734409266665</v>
+        <v>0.6667516724349682</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090463415421334</v>
+        <v>1.090451215192652</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.02740343787273</v>
+        <v>10.99716770554933</v>
       </c>
       <c r="E7" t="n">
-        <v>153.4963656940443</v>
+        <v>155.0376788619032</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2892651947487902</v>
+        <v>-0.2904783447469692</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7118796223224992</v>
+        <v>0.7118698894079755</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4063400407572642</v>
+        <v>-0.4080497701462618</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7506652775131005</v>
+        <v>0.750759536199234</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075551069233559</v>
+        <v>1.075718111376672</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.09782745562311</v>
+        <v>10.10318224686997</v>
       </c>
       <c r="E8" t="n">
-        <v>247.4292765042955</v>
+        <v>246.9874035330145</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3022700873725092</v>
+        <v>-0.298883810021418</v>
       </c>
       <c r="G8" t="n">
-        <v>1.167413122349056</v>
+        <v>1.167372765063212</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2589229824351164</v>
+        <v>-0.2560311658506388</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7374683580992097</v>
+        <v>0.7374457564491324</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732790702730913</v>
+        <v>1.732752912856327</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.36060542201128</v>
+        <v>7.329245128060283</v>
       </c>
       <c r="E9" t="n">
-        <v>186.3050406587133</v>
+        <v>188.594617128212</v>
       </c>
       <c r="F9" t="n">
-        <v>0.417252185388594</v>
+        <v>0.4096056239058321</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4801633185249929</v>
+        <v>0.4803571434342026</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8689797185473169</v>
+        <v>0.8527105914933443</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.676337423674767</v>
+        <v>0.6759568652505755</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6536278457524182</v>
+        <v>0.6535521332072127</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.952366649239971</v>
+        <v>6.953114237766297</v>
       </c>
       <c r="E10" t="n">
-        <v>597.4403578615437</v>
+        <v>598.8895148442269</v>
       </c>
       <c r="F10" t="n">
-        <v>1.064631234710496</v>
+        <v>1.071676579832428</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8190414646223692</v>
+        <v>0.8190391381832071</v>
       </c>
       <c r="H10" t="n">
-        <v>1.299850228219348</v>
+        <v>1.308455884305629</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6637240409748977</v>
+        <v>0.6637203689351748</v>
       </c>
       <c r="N10" t="n">
-        <v>1.094136697795762</v>
+        <v>1.094175033376022</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.631409961288135</v>
+        <v>6.642765641089055</v>
       </c>
       <c r="E11" t="n">
-        <v>195.9815026282848</v>
+        <v>195.862016927218</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2750846245505572</v>
+        <v>-0.271383989118775</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9551089985226601</v>
+        <v>0.9550566421420563</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2880138549380767</v>
+        <v>-0.2841548628048901</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7133402931249181</v>
+        <v>0.7133099754120108</v>
       </c>
       <c r="N11" t="n">
-        <v>1.371285361368968</v>
+        <v>1.371211435963505</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.319146997577179</v>
+        <v>6.326983262478038</v>
       </c>
       <c r="E12" t="n">
-        <v>76.1146518267694</v>
+        <v>77.15925209559506</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2744996004135839</v>
+        <v>-0.2715093683101761</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6560322263919859</v>
+        <v>0.6560009966210499</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4184239574986482</v>
+        <v>-0.4138856033888286</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7888407850640553</v>
+        <v>0.7888216619513315</v>
       </c>
       <c r="N12" t="n">
-        <v>1.04158010918978</v>
+        <v>1.041550489283023</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.728459316104344</v>
+        <v>4.746336060112006</v>
       </c>
       <c r="E13" t="n">
-        <v>148.6808055670004</v>
+        <v>153.3701342203222</v>
       </c>
       <c r="F13" t="n">
-        <v>1.722941693880423</v>
+        <v>1.742539707774409</v>
       </c>
       <c r="G13" t="n">
-        <v>0.857941154171362</v>
+        <v>0.8579602617396541</v>
       </c>
       <c r="H13" t="n">
-        <v>2.008228286407962</v>
+        <v>2.031026127295367</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6033457975642775</v>
+        <v>0.6033132524934687</v>
       </c>
       <c r="N13" t="n">
-        <v>1.041842189222357</v>
+        <v>1.041854418789949</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.58829966462755</v>
+        <v>4.598356503685597</v>
       </c>
       <c r="E14" t="n">
-        <v>60.32526692037459</v>
+        <v>60.43891488004016</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3954747466752417</v>
+        <v>-0.3930245189393603</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8471467191951157</v>
+        <v>0.8471628992099961</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4668314681676239</v>
+        <v>-0.4639302775249802</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601178715108391</v>
+        <v>0.7601253618535561</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296037966434007</v>
+        <v>1.296131755011982</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.362660514720453</v>
+        <v>4.356286611308648</v>
       </c>
       <c r="E15" t="n">
-        <v>155.9630991544506</v>
+        <v>161.3955602854318</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6152181223323197</v>
+        <v>0.6165806069762938</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9572431688649938</v>
+        <v>0.9572457849808413</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6426978455869115</v>
+        <v>0.6441194274766477</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5137228796511476</v>
+        <v>0.5137557731557272</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9897587077964273</v>
+        <v>0.9898677557121003</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.174382532050514</v>
+        <v>4.167877284928682</v>
       </c>
       <c r="E16" t="n">
-        <v>132.6044112776335</v>
+        <v>133.899861068397</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.01976168993488692</v>
+        <v>-0.020611223619866</v>
       </c>
       <c r="G16" t="n">
-        <v>0.79156963644908</v>
+        <v>0.7915846233586186</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.02496519450081022</v>
+        <v>-0.02603792824122143</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.713663848474843</v>
+        <v>0.7135845507749243</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137001327400801</v>
+        <v>1.13694586912188</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.697122049157884</v>
+        <v>3.698477657743954</v>
       </c>
       <c r="E17" t="n">
-        <v>113.6986572024783</v>
+        <v>115.2090635135058</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1030836896658011</v>
+        <v>-0.1062702949432099</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7534229365038544</v>
+        <v>0.753360398737175</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1368204824559037</v>
+        <v>-0.1410616952010567</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7211244881016805</v>
+        <v>0.7213540004101858</v>
       </c>
       <c r="N17" t="n">
-        <v>1.093521253219353</v>
+        <v>1.093825973317198</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.130276284033723</v>
+        <v>3.132170938349383</v>
       </c>
       <c r="E18" t="n">
-        <v>44.07111596085822</v>
+        <v>44.42416110032298</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.462859039986022</v>
+        <v>-0.4606181127347629</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7432261850188765</v>
+        <v>0.7431997339269258</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6227700924911119</v>
+        <v>-0.6197770151247829</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7644657513648043</v>
+        <v>0.7644474973704786</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143555330991084</v>
+        <v>1.143536966816692</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.972566338381673</v>
+        <v>2.971213617051924</v>
       </c>
       <c r="E19" t="n">
-        <v>52.50145548897815</v>
+        <v>49.96527619350025</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1155425308376925</v>
+        <v>0.1146202868788488</v>
       </c>
       <c r="G19" t="n">
-        <v>0.479529333982196</v>
+        <v>0.4795392402035885</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2409498703200968</v>
+        <v>0.2390217051480225</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7177957610405643</v>
+        <v>0.7177526480349929</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6927782041498399</v>
+        <v>0.6927809771794124</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.628221986259251</v>
+        <v>2.629184964307644</v>
       </c>
       <c r="E20" t="n">
-        <v>75.32567388878741</v>
+        <v>75.32721654705361</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3070618933816294</v>
+        <v>-0.3050451860124402</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7755818472602986</v>
+        <v>0.7755548219301212</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3959116558314369</v>
+        <v>-0.3933251104715913</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7325915878483626</v>
+        <v>0.7325659234598317</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143583051903783</v>
+        <v>1.143552782611186</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-30.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-30.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>570.1762349451532</v>
+        <v>569.9334322345941</v>
       </c>
       <c r="E2" t="n">
-        <v>6050.688792153733</v>
+        <v>5942.5555259865</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6178829152401264</v>
+        <v>0.6163580904344561</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4968244955197113</v>
+        <v>0.4968299291994258</v>
       </c>
       <c r="H2" t="n">
-        <v>1.243664353936051</v>
+        <v>1.240581644160677</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>227.0418270726495</v>
+        <v>226.8645751470141</v>
       </c>
       <c r="E3" t="n">
-        <v>2598.917505811584</v>
+        <v>2581.608428342793</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2678067121424503</v>
+        <v>0.2659216780285012</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5956453510446934</v>
+        <v>0.5956542201175214</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4496076594449167</v>
+        <v>0.4464363200113572</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907046091411581</v>
+        <v>0.890707309255758</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067870172210465</v>
+        <v>1.067877630686681</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.95162301962845</v>
+        <v>37.93335065206863</v>
       </c>
       <c r="E4" t="n">
-        <v>957.7764646834712</v>
+        <v>982.1010181083998</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8023939008828924</v>
+        <v>0.8000424965089163</v>
       </c>
       <c r="G4" t="n">
-        <v>1.104488423127185</v>
+        <v>1.104479578190417</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7264846639234481</v>
+        <v>0.7243615113461024</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4735095636840184</v>
+        <v>0.4735023578027076</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052657097315472</v>
+        <v>1.05262113589011</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.27671227609543</v>
+        <v>37.31081325427192</v>
       </c>
       <c r="E5" t="n">
-        <v>378.3638336194885</v>
+        <v>379.582463704907</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3276240283829599</v>
+        <v>-0.3268791695108052</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5593903845380145</v>
+        <v>0.5593916507391873</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5856804790335032</v>
+        <v>-0.5843476016827618</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7362269145173652</v>
+        <v>0.7362036086421359</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8289411261582315</v>
+        <v>0.828907696003888</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.24806583385351</v>
+        <v>11.24106414641669</v>
       </c>
       <c r="E6" t="n">
-        <v>497.9088632434308</v>
+        <v>496.238999227868</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4607223926955714</v>
+        <v>-0.4599992389102436</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8125407063448896</v>
+        <v>0.8125395314323708</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5670145373615459</v>
+        <v>-0.5661253651245032</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6667516724349682</v>
+        <v>0.6667375075569651</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090451215192652</v>
+        <v>1.090414546586758</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.99716770554933</v>
+        <v>10.98638552578344</v>
       </c>
       <c r="E7" t="n">
-        <v>155.0376788619032</v>
+        <v>155.1750222469757</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2904783447469692</v>
+        <v>-0.2935089075460661</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7118698894079755</v>
+        <v>0.7118588412816491</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4080497701462618</v>
+        <v>-0.4123133555771044</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.750759536199234</v>
+        <v>0.7507928409257872</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075718111376672</v>
+        <v>1.075737370824652</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.10318224686997</v>
+        <v>10.06685995561357</v>
       </c>
       <c r="E8" t="n">
-        <v>246.9874035330145</v>
+        <v>240.902003002923</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.298883810021418</v>
+        <v>-0.3030220258381484</v>
       </c>
       <c r="G8" t="n">
-        <v>1.167372765063212</v>
+        <v>1.167424058927925</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2560311658506388</v>
+        <v>-0.2595646573503215</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7374457564491324</v>
+        <v>0.7374508526822594</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732752912856327</v>
+        <v>1.732822072706922</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.329245128060283</v>
+        <v>7.289193957827908</v>
       </c>
       <c r="E9" t="n">
-        <v>188.594617128212</v>
+        <v>190.3924265901335</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4096056239058321</v>
+        <v>0.3985022008661927</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4803571434342026</v>
+        <v>0.480716220557805</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8527105914933443</v>
+        <v>0.8289759817211613</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6759568652505755</v>
+        <v>0.6756253664879999</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6535521332072127</v>
+        <v>0.6537127769545583</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.953114237766297</v>
+        <v>6.938443593002864</v>
       </c>
       <c r="E10" t="n">
-        <v>598.8895148442269</v>
+        <v>594.755505615408</v>
       </c>
       <c r="F10" t="n">
-        <v>1.071676579832428</v>
+        <v>1.061110856635221</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8190391381832071</v>
+        <v>0.8190465513264715</v>
       </c>
       <c r="H10" t="n">
-        <v>1.308455884305629</v>
+        <v>1.295544013849663</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6637203689351748</v>
+        <v>0.6637459262495475</v>
       </c>
       <c r="N10" t="n">
-        <v>1.094175033376022</v>
+        <v>1.09421510239467</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.642765641089055</v>
+        <v>6.624912419531189</v>
       </c>
       <c r="E11" t="n">
-        <v>195.862016927218</v>
+        <v>191.885621935136</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.271383989118775</v>
+        <v>-0.2759063355739786</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9550566421420563</v>
+        <v>0.9551232902809995</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2841548628048901</v>
+        <v>-0.2888698646358067</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7133099754120108</v>
+        <v>0.7133101282538181</v>
       </c>
       <c r="N11" t="n">
-        <v>1.371211435963505</v>
+        <v>1.371292421506026</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.326983262478038</v>
+        <v>6.317823687800654</v>
       </c>
       <c r="E12" t="n">
-        <v>77.15925209559506</v>
+        <v>76.69328788018697</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2715093683101761</v>
+        <v>-0.2735654895602816</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6560009966210499</v>
+        <v>0.6560204527792576</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4138856033888286</v>
+        <v>-0.4170075618851671</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7888216619513315</v>
+        <v>0.7888274896463338</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041550489283023</v>
+        <v>1.041577683849227</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.746336060112006</v>
+        <v>4.740654326754504</v>
       </c>
       <c r="E13" t="n">
-        <v>153.3701342203222</v>
+        <v>154.5939301786537</v>
       </c>
       <c r="F13" t="n">
-        <v>1.742539707774409</v>
+        <v>1.734997772702385</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8579602617396541</v>
+        <v>0.857947635703564</v>
       </c>
       <c r="H13" t="n">
-        <v>2.031026127295367</v>
+        <v>2.022265346392139</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6033132524934687</v>
+        <v>0.6033255684378199</v>
       </c>
       <c r="N13" t="n">
-        <v>1.041854418789949</v>
+        <v>1.041848959934466</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.598356503685597</v>
+        <v>4.59088326688673</v>
       </c>
       <c r="E14" t="n">
-        <v>60.43891488004016</v>
+        <v>59.98197180052642</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3930245189393603</v>
+        <v>-0.3948624265255022</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8471628992099961</v>
+        <v>0.8471494253380977</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4639302775249802</v>
+        <v>-0.4661071762728428</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601253618535561</v>
+        <v>0.7601414688759659</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296131755011982</v>
+        <v>1.296124429483497</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.356286611308648</v>
+        <v>4.378086679661629</v>
       </c>
       <c r="E15" t="n">
-        <v>161.3955602854318</v>
+        <v>165.8804608905185</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6165806069762938</v>
+        <v>0.6370529272130212</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9572457849808413</v>
+        <v>0.9573512317661197</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6441194274766477</v>
+        <v>0.6654328172094031</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5137557731557272</v>
+        <v>0.513601216573194</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9898677557121003</v>
+        <v>0.9896681508604517</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.167877284928682</v>
+        <v>4.159964628073171</v>
       </c>
       <c r="E16" t="n">
-        <v>133.899861068397</v>
+        <v>135.8384587072051</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.020611223619866</v>
+        <v>-0.0243469406968615</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7915846233586186</v>
+        <v>0.7916586366109598</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.02603792824122143</v>
+        <v>-0.03075434230224431</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7135845507749243</v>
+        <v>0.7135747350963817</v>
       </c>
       <c r="N16" t="n">
-        <v>1.13694586912188</v>
+        <v>1.137024097595531</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.698477657743954</v>
+        <v>3.702015339314793</v>
       </c>
       <c r="E17" t="n">
-        <v>115.2090635135058</v>
+        <v>116.5430028206052</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1062702949432099</v>
+        <v>-0.1038337390844559</v>
       </c>
       <c r="G17" t="n">
-        <v>0.753360398737175</v>
+        <v>0.7534070797697237</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1410616952010567</v>
+        <v>-0.1378189054397954</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7213540004101858</v>
+        <v>0.7212482170679176</v>
       </c>
       <c r="N17" t="n">
-        <v>1.093825973317198</v>
+        <v>1.093721374406459</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.132170938349383</v>
+        <v>3.127602268565456</v>
       </c>
       <c r="E18" t="n">
-        <v>44.42416110032298</v>
+        <v>44.58902997935802</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4606181127347629</v>
+        <v>-0.462459048786604</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7431997339269258</v>
+        <v>0.7432202188853764</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6197770151247829</v>
+        <v>-0.6222369050725827</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7644474973704786</v>
+        <v>0.7644558829883196</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143536966816692</v>
+        <v>1.143568523736692</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.971213617051924</v>
+        <v>2.973749140298641</v>
       </c>
       <c r="E19" t="n">
-        <v>49.96527619350025</v>
+        <v>48.64904499217121</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1146202868788488</v>
+        <v>0.1164649691029389</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4795392402035885</v>
+        <v>0.4795204651299567</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2390217051480225</v>
+        <v>0.2428779949389132</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7177526480349929</v>
+        <v>0.717774729923646</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6927809771794124</v>
+        <v>0.6927675893159813</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.629184964307644</v>
+        <v>2.625992760339494</v>
       </c>
       <c r="E20" t="n">
-        <v>75.32721654705361</v>
+        <v>75.15402131624096</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3050451860124402</v>
+        <v>-0.3075658368109843</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7755548219301212</v>
+        <v>0.7755898352709342</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3933251104715913</v>
+        <v>-0.3965573333017487</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7325659234598317</v>
+        <v>0.7325700694950087</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143552782611186</v>
+        <v>1.143598374678405</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-30.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-30.xlsx
@@ -579,19 +579,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>572.3463608888128</v>
+        <v>570.2615835949629</v>
       </c>
       <c r="E2">
-        <v>6474.382614262471</v>
+        <v>6613.889114995178</v>
       </c>
       <c r="F2">
-        <v>0.625964667456413</v>
+        <v>0.6195465762411225</v>
       </c>
       <c r="G2">
-        <v>0.4968175936810127</v>
+        <v>0.4968200646910677</v>
       </c>
       <c r="H2">
-        <v>1.25994867214449</v>
+        <v>1.247024064187844</v>
       </c>
       <c r="I2">
         <v>0.2590724514387045</v>
@@ -623,19 +623,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>227.6701530109772</v>
+        <v>226.8054736708407</v>
       </c>
       <c r="E3">
-        <v>2774.308167648749</v>
+        <v>2826.495503631028</v>
       </c>
       <c r="F3">
-        <v>0.2725314947481035</v>
+        <v>0.2673897680540887</v>
       </c>
       <c r="G3">
-        <v>0.5956350685581695</v>
+        <v>0.5956470783545122</v>
       </c>
       <c r="H3">
-        <v>0.4575477656273829</v>
+        <v>0.4489063705185268</v>
       </c>
       <c r="I3">
         <v>0.3295577524045769</v>
@@ -650,10 +650,10 @@
         <v>50</v>
       </c>
       <c r="M3">
-        <v>0.8906959564427582</v>
+        <v>0.8907014668728902</v>
       </c>
       <c r="N3">
-        <v>1.067856198790132</v>
+        <v>1.067879025294233</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -667,19 +667,19 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>37.90999514711408</v>
+        <v>37.75044247103453</v>
       </c>
       <c r="E4">
-        <v>1049.779024683747</v>
+        <v>1063.175638598855</v>
       </c>
       <c r="F4">
-        <v>0.7980276297368094</v>
+        <v>0.785615338699112</v>
       </c>
       <c r="G4">
-        <v>1.104472918399724</v>
+        <v>1.104450648428243</v>
       </c>
       <c r="H4">
-        <v>0.72254160010829</v>
+        <v>0.7113177395632214</v>
       </c>
       <c r="I4">
         <v>0.3422195892575038</v>
@@ -694,10 +694,10 @@
         <v>50</v>
       </c>
       <c r="M4">
-        <v>0.4735893974951512</v>
+        <v>0.4735750688693525</v>
       </c>
       <c r="N4">
-        <v>1.05283442178273</v>
+        <v>1.052776103592842</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -711,19 +711,19 @@
         <v>16</v>
       </c>
       <c r="D5">
-        <v>37.44113815659149</v>
+        <v>37.40147238525294</v>
       </c>
       <c r="E5">
-        <v>380.9165613656429</v>
+        <v>406.7038488625988</v>
       </c>
       <c r="F5">
-        <v>-0.3227786937335113</v>
+        <v>-0.3250161035158924</v>
       </c>
       <c r="G5">
-        <v>0.559427404806372</v>
+        <v>0.5594018629207999</v>
       </c>
       <c r="H5">
-        <v>-0.5769804821149778</v>
+        <v>-0.5810064732693037</v>
       </c>
       <c r="I5">
         <v>0.3496897913141569</v>
@@ -738,10 +738,10 @@
         <v>50</v>
       </c>
       <c r="M5">
-        <v>0.7362222604600647</v>
+        <v>0.736194618365602</v>
       </c>
       <c r="N5">
-        <v>0.829002261128248</v>
+        <v>0.8289291642077057</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -755,19 +755,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>11.18204904965573</v>
+        <v>11.13501845457639</v>
       </c>
       <c r="E6">
-        <v>532.5988413568242</v>
+        <v>532.3567766836671</v>
       </c>
       <c r="F6">
-        <v>-0.4653266848720492</v>
+        <v>-0.4681204491106474</v>
       </c>
       <c r="G6">
-        <v>0.8125862672508738</v>
+        <v>0.812646119638597</v>
       </c>
       <c r="H6">
-        <v>-0.5726489649478491</v>
+        <v>-0.5760446494457289</v>
       </c>
       <c r="I6">
         <v>0.5751178664414889</v>
@@ -782,10 +782,10 @@
         <v>50</v>
       </c>
       <c r="M6">
-        <v>0.6666844571911759</v>
+        <v>0.6667280353589129</v>
       </c>
       <c r="N6">
-        <v>1.090417572552758</v>
+        <v>1.090563745901841</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -799,19 +799,19 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>11.0351977133425</v>
+        <v>11.01963530703672</v>
       </c>
       <c r="E7">
-        <v>160.0337556058037</v>
+        <v>161.884326521974</v>
       </c>
       <c r="F7">
-        <v>-0.2868373116802418</v>
+        <v>-0.2907815497200198</v>
       </c>
       <c r="G7">
-        <v>0.7119081966315819</v>
+        <v>0.7118679306033032</v>
       </c>
       <c r="H7">
-        <v>-0.4029133433740789</v>
+        <v>-0.4084768216396325</v>
       </c>
       <c r="I7">
         <v>0.4277673545966229</v>
@@ -826,10 +826,10 @@
         <v>50</v>
       </c>
       <c r="M7">
-        <v>0.7507943169144431</v>
+        <v>0.750780342200046</v>
       </c>
       <c r="N7">
-        <v>1.075840781393465</v>
+        <v>1.075754556877492</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -843,19 +843,19 @@
         <v>36</v>
       </c>
       <c r="D8">
-        <v>10.1203851060239</v>
+        <v>10.08434826264828</v>
       </c>
       <c r="E8">
-        <v>259.3839793527437</v>
+        <v>264.4174221139738</v>
       </c>
       <c r="F8">
-        <v>-0.2962471536529508</v>
+        <v>-0.3026460824286126</v>
       </c>
       <c r="G8">
-        <v>1.167351397122762</v>
+        <v>1.167418501174469</v>
       </c>
       <c r="H8">
-        <v>-0.2537771868720321</v>
+        <v>-0.2592438633824448</v>
       </c>
       <c r="I8">
         <v>0.7387533875338753</v>
@@ -870,10 +870,10 @@
         <v>50</v>
       </c>
       <c r="M8">
-        <v>0.7374075944949128</v>
+        <v>0.7374254028575749</v>
       </c>
       <c r="N8">
-        <v>1.732655599622879</v>
+        <v>1.732788427269506</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -887,19 +887,19 @@
         <v>37</v>
       </c>
       <c r="D9">
-        <v>7.293587266190028</v>
+        <v>7.277967874967039</v>
       </c>
       <c r="E9">
-        <v>198.5281554482387</v>
+        <v>199.7459228351568</v>
       </c>
       <c r="F9">
-        <v>0.4017383875443306</v>
+        <v>0.4065962383606763</v>
       </c>
       <c r="G9">
-        <v>0.4806020536495886</v>
+        <v>0.4804453707602968</v>
       </c>
       <c r="H9">
-        <v>0.8359065145344586</v>
+        <v>0.8462902612991036</v>
       </c>
       <c r="I9">
         <v>0.2154834665412946</v>
@@ -914,10 +914,10 @@
         <v>50</v>
       </c>
       <c r="M9">
-        <v>0.6751892205429838</v>
+        <v>0.6757705653476709</v>
       </c>
       <c r="N9">
-        <v>0.6531518410826856</v>
+        <v>0.6534978413547845</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -931,19 +931,19 @@
         <v>38</v>
       </c>
       <c r="D10">
-        <v>6.967366362348528</v>
+        <v>6.947888917884047</v>
       </c>
       <c r="E10">
-        <v>615.1583541905333</v>
+        <v>617.7675334519056</v>
       </c>
       <c r="F10">
-        <v>1.079021978156511</v>
+        <v>1.069621055884787</v>
       </c>
       <c r="G10">
-        <v>0.8190478404621017</v>
+        <v>0.8190387359462802</v>
       </c>
       <c r="H10">
-        <v>1.317410198588319</v>
+        <v>1.305946848348992</v>
       </c>
       <c r="I10">
         <v>0.3268819295856837</v>
@@ -958,10 +958,10 @@
         <v>50</v>
       </c>
       <c r="M10">
-        <v>0.6637410905258215</v>
+        <v>0.6637326940577906</v>
       </c>
       <c r="N10">
-        <v>1.094236020897001</v>
+        <v>1.094204573008433</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -975,19 +975,19 @@
         <v>39</v>
       </c>
       <c r="D11">
-        <v>6.631790595127649</v>
+        <v>6.609691052032476</v>
       </c>
       <c r="E11">
-        <v>191.578129734891</v>
+        <v>194.0926457947774</v>
       </c>
       <c r="F11">
-        <v>-0.2728922349286476</v>
+        <v>-0.2780964033804886</v>
       </c>
       <c r="G11">
-        <v>0.9550756106235556</v>
+        <v>0.9551661246454288</v>
       </c>
       <c r="H11">
-        <v>-0.2857284092413165</v>
+        <v>-0.2911497761540924</v>
       </c>
       <c r="I11">
         <v>0.6126386245816655</v>
@@ -1002,10 +1002,10 @@
         <v>50</v>
       </c>
       <c r="M11">
-        <v>0.7132160030266401</v>
+        <v>0.7132511673023336</v>
       </c>
       <c r="N11">
-        <v>1.371077067843366</v>
+        <v>1.371267792484643</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1019,19 +1019,19 @@
         <v>40</v>
       </c>
       <c r="D12">
-        <v>6.422544823738298</v>
+        <v>6.416604985788151</v>
       </c>
       <c r="E12">
-        <v>81.45964055500613</v>
+        <v>82.46109773679497</v>
       </c>
       <c r="F12">
-        <v>-0.2666435669002752</v>
+        <v>-0.2675799387003731</v>
       </c>
       <c r="G12">
-        <v>0.6559902445614365</v>
+        <v>0.65598846629226</v>
       </c>
       <c r="H12">
-        <v>-0.4064748967090818</v>
+        <v>-0.4079034197243938</v>
       </c>
       <c r="I12">
         <v>0.4207389749702026</v>
@@ -1046,10 +1046,10 @@
         <v>50</v>
       </c>
       <c r="M12">
-        <v>0.788815289120564</v>
+        <v>0.7888036324989671</v>
       </c>
       <c r="N12">
-        <v>1.041539472445167</v>
+        <v>1.04151607767798</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1063,19 +1063,19 @@
         <v>41</v>
       </c>
       <c r="D13">
-        <v>4.957153530657654</v>
+        <v>4.931784496446302</v>
       </c>
       <c r="E13">
-        <v>274.6923098876744</v>
+        <v>303.637401006557</v>
       </c>
       <c r="F13">
-        <v>1.902131122351304</v>
+        <v>1.883776121363141</v>
       </c>
       <c r="G13">
-        <v>0.8597472677947414</v>
+        <v>0.8593962579487361</v>
       </c>
       <c r="H13">
-        <v>2.212430552097346</v>
+        <v>2.191976173900807</v>
       </c>
       <c r="I13">
         <v>0.3000688231245698</v>
@@ -1090,10 +1090,10 @@
         <v>50</v>
       </c>
       <c r="M13">
-        <v>0.6022813765851497</v>
+        <v>0.6021089654634717</v>
       </c>
       <c r="N13">
-        <v>1.04225328279176</v>
+        <v>1.041524343664447</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1107,19 +1107,19 @@
         <v>42</v>
       </c>
       <c r="D14">
-        <v>4.619745174064216</v>
+        <v>4.602384805113891</v>
       </c>
       <c r="E14">
-        <v>65.40939641184102</v>
+        <v>67.22184495341749</v>
       </c>
       <c r="F14">
-        <v>-0.3893444486799922</v>
+        <v>-0.3936373125792902</v>
       </c>
       <c r="G14">
-        <v>0.8472139448521336</v>
+        <v>0.8471575153583234</v>
       </c>
       <c r="H14">
-        <v>-0.4595585932523165</v>
+        <v>-0.4646565785499677</v>
       </c>
       <c r="I14">
         <v>0.4691011235955056</v>
@@ -1134,10 +1134,10 @@
         <v>50</v>
       </c>
       <c r="M14">
-        <v>0.7601643860200781</v>
+        <v>0.760153111087419</v>
       </c>
       <c r="N14">
-        <v>1.296294407459475</v>
+        <v>1.296182394084969</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1151,19 +1151,19 @@
         <v>43</v>
       </c>
       <c r="D15">
-        <v>4.336674885575214</v>
+        <v>4.326684438503555</v>
       </c>
       <c r="E15">
-        <v>181.9153836236416</v>
+        <v>183.0252116455603</v>
       </c>
       <c r="F15">
-        <v>0.6124940314801188</v>
+        <v>0.602968949821461</v>
       </c>
       <c r="G15">
-        <v>0.9572395918967149</v>
+        <v>0.9572444529480665</v>
       </c>
       <c r="H15">
-        <v>0.6398544697325956</v>
+        <v>0.6299006987864718</v>
       </c>
       <c r="I15">
         <v>0.3858131487889274</v>
@@ -1178,10 +1178,10 @@
         <v>50</v>
       </c>
       <c r="M15">
-        <v>0.5137943586169349</v>
+        <v>0.513799591993835</v>
       </c>
       <c r="N15">
-        <v>0.9899494470743128</v>
+        <v>0.989959633914763</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1195,19 +1195,19 @@
         <v>44</v>
       </c>
       <c r="D16">
-        <v>4.188881538934218</v>
+        <v>4.172509046072678</v>
       </c>
       <c r="E16">
-        <v>143.3375841124926</v>
+        <v>144.8042520224251</v>
       </c>
       <c r="F16">
-        <v>-0.0100637633150793</v>
+        <v>-0.02315869806192372</v>
       </c>
       <c r="G16">
-        <v>0.791446817227701</v>
+        <v>0.7916336603926114</v>
       </c>
       <c r="H16">
-        <v>-0.01271565327703369</v>
+        <v>-0.02925431196348845</v>
       </c>
       <c r="I16">
         <v>0.4268646717284502</v>
@@ -1222,10 +1222,10 @@
         <v>50</v>
       </c>
       <c r="M16">
-        <v>0.7135697525723229</v>
+        <v>0.7135211972519842</v>
       </c>
       <c r="N16">
-        <v>1.13674015720532</v>
+        <v>1.136925493336385</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1239,19 +1239,19 @@
         <v>45</v>
       </c>
       <c r="D17">
-        <v>3.696089224083612</v>
+        <v>3.692607238674999</v>
       </c>
       <c r="E17">
-        <v>117.3003168007247</v>
+        <v>118.1599511806155</v>
       </c>
       <c r="F17">
-        <v>-0.1066449996268219</v>
+        <v>-0.1102026959434957</v>
       </c>
       <c r="G17">
-        <v>0.7533538759261401</v>
+        <v>0.7533006736727427</v>
       </c>
       <c r="H17">
-        <v>-0.1415602985990047</v>
+        <v>-0.146293106849618</v>
       </c>
       <c r="I17">
         <v>0.4720416124837452</v>
@@ -1266,10 +1266,10 @@
         <v>50</v>
       </c>
       <c r="M17">
-        <v>0.7215253259508052</v>
+        <v>0.7214708549791402</v>
       </c>
       <c r="N17">
-        <v>1.094091489104776</v>
+        <v>1.093926191223749</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1283,19 +1283,19 @@
         <v>46</v>
       </c>
       <c r="D18">
-        <v>3.148477279284114</v>
+        <v>3.143518321463928</v>
       </c>
       <c r="E18">
-        <v>47.50800245950783</v>
+        <v>48.02038374064009</v>
       </c>
       <c r="F18">
-        <v>-0.4566907788119633</v>
+        <v>-0.4585351252806213</v>
       </c>
       <c r="G18">
-        <v>0.7431942192558151</v>
+        <v>0.7431903450179421</v>
       </c>
       <c r="H18">
-        <v>-0.6144972161775731</v>
+        <v>-0.6169820805052996</v>
       </c>
       <c r="I18">
         <v>0.4644343302990898</v>
@@ -1310,10 +1310,10 @@
         <v>50</v>
       </c>
       <c r="M18">
-        <v>0.7644426590128305</v>
+        <v>0.764436613715902</v>
       </c>
       <c r="N18">
-        <v>1.143537129837744</v>
+        <v>1.143516437978683</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1327,19 +1327,19 @@
         <v>47</v>
       </c>
       <c r="D19">
-        <v>2.978905779867103</v>
+        <v>2.974525209436718</v>
       </c>
       <c r="E19">
-        <v>44.78159655801142</v>
+        <v>44.43757104560514</v>
       </c>
       <c r="F19">
-        <v>0.1201566636542351</v>
+        <v>0.1155425308376925</v>
       </c>
       <c r="G19">
-        <v>0.4794953644627805</v>
+        <v>0.479529333982196</v>
       </c>
       <c r="H19">
-        <v>0.2505898337283339</v>
+        <v>0.2409498703200968</v>
       </c>
       <c r="I19">
         <v>0.2812667740203972</v>
@@ -1354,10 +1354,10 @@
         <v>50</v>
       </c>
       <c r="M19">
-        <v>0.7177248181571625</v>
+        <v>0.7177415808504168</v>
       </c>
       <c r="N19">
-        <v>0.6927003545031745</v>
+        <v>0.6927621621935612</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1371,19 +1371,19 @@
         <v>48</v>
       </c>
       <c r="D20">
-        <v>2.712656250474298</v>
+        <v>2.688908047755418</v>
       </c>
       <c r="E20">
-        <v>133.1995201665432</v>
+        <v>141.8635252264938</v>
       </c>
       <c r="F20">
-        <v>-0.2761459706685456</v>
+        <v>-0.2863201756665339</v>
       </c>
       <c r="G20">
-        <v>0.776026210266585</v>
+        <v>0.7756785757479153</v>
       </c>
       <c r="H20">
-        <v>-0.3558461905219443</v>
+        <v>-0.3691221913541466</v>
       </c>
       <c r="I20">
         <v>0.443815987933635</v>
@@ -1398,10 +1398,10 @@
         <v>50</v>
       </c>
       <c r="M20">
-        <v>0.7321729202989959</v>
+        <v>0.732316813152378</v>
       </c>
       <c r="N20">
-        <v>1.143649870347099</v>
+        <v>1.143356524812476</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-30.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-30.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>572.3463608888128</v>
+        <v>567.4935324880297</v>
       </c>
       <c r="E2" t="n">
-        <v>6474.382614262471</v>
+        <v>7889.367504535481</v>
       </c>
       <c r="F2" t="n">
-        <v>0.625964667456413</v>
+        <v>0.6048006168441964</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4968175936810127</v>
+        <v>0.4969138938027969</v>
       </c>
       <c r="H2" t="n">
-        <v>1.25994867214449</v>
+        <v>1.217113516822323</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>227.6701530109772</v>
+        <v>224.9495154108557</v>
       </c>
       <c r="E3" t="n">
-        <v>2774.308167648749</v>
+        <v>3606.930637494635</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2725314947481035</v>
+        <v>0.2478961079873427</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5956350685581695</v>
+        <v>0.595876977718001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4575477656273829</v>
+        <v>0.4160189389036266</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,45 +598,45 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8906959564427582</v>
+        <v>0.8907295078499181</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067856198790132</v>
+        <v>1.068123096820651</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.90999514711408</v>
+        <v>37.17781422738018</v>
       </c>
       <c r="E4" t="n">
-        <v>1049.779024683747</v>
+        <v>445.424252837517</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7980276297368094</v>
+        <v>-0.3306013608702448</v>
       </c>
       <c r="G4" t="n">
-        <v>1.104472918399724</v>
+        <v>0.5594014265704497</v>
       </c>
       <c r="H4" t="n">
-        <v>0.72254160010829</v>
+        <v>-0.5909912723982117</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3422195892575038</v>
+        <v>0.3496897913141569</v>
       </c>
       <c r="J4" t="n">
         <v>272</v>
@@ -652,45 +652,45 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4735893974951512</v>
+        <v>0.736208017526488</v>
       </c>
       <c r="N4" t="n">
-        <v>1.05283442178273</v>
+        <v>0.8287870804038321</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.44113815659149</v>
+        <v>36.89474913854026</v>
       </c>
       <c r="E5" t="n">
-        <v>380.9165613656429</v>
+        <v>1246.25039644709</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3227786937335113</v>
+        <v>0.7325267588529449</v>
       </c>
       <c r="G5" t="n">
-        <v>0.559427404806372</v>
+        <v>1.104723151079294</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5769804821149778</v>
+        <v>0.6630862747261881</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3496897913141569</v>
+        <v>0.3422195892575038</v>
       </c>
       <c r="J5" t="n">
         <v>272</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7362222604600647</v>
+        <v>0.4738148328705722</v>
       </c>
       <c r="N5" t="n">
-        <v>0.829002261128248</v>
+        <v>1.053370054097573</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.18204904965573</v>
+        <v>10.89403411519803</v>
       </c>
       <c r="E6" t="n">
-        <v>532.5988413568242</v>
+        <v>458.6166819497926</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4653266848720492</v>
+        <v>-0.484000124591757</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8125862672508738</v>
+        <v>0.8134532072756746</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5726489649478491</v>
+        <v>-0.5949944265543133</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6666844571911759</v>
+        <v>0.6668151763635847</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090417572552758</v>
+        <v>1.091583372165312</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.0351977133425</v>
+        <v>10.8145519491741</v>
       </c>
       <c r="E7" t="n">
-        <v>160.0337556058037</v>
+        <v>176.5028974099286</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2868373116802418</v>
+        <v>-0.3055980018791926</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7119081966315819</v>
+        <v>0.7120044138093254</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4029133433740789</v>
+        <v>-0.4292080160629899</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7507943169144431</v>
+        <v>0.750917551930409</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075840781393465</v>
+        <v>1.075954240863964</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.1203851060239</v>
+        <v>9.74182892171579</v>
       </c>
       <c r="E8" t="n">
-        <v>259.3839793527437</v>
+        <v>338.1055048091164</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2962471536529508</v>
+        <v>-0.3336723127099466</v>
       </c>
       <c r="G8" t="n">
-        <v>1.167351397122762</v>
+        <v>1.168488284969429</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2537771868720321</v>
+        <v>-0.2855589713667318</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7374075944949128</v>
+        <v>0.7374441989286451</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732655599622879</v>
+        <v>1.734093004871293</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.293587266190028</v>
+        <v>7.154286794179395</v>
       </c>
       <c r="E9" t="n">
-        <v>198.5281554482387</v>
+        <v>224.6768150091932</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4017383875443306</v>
+        <v>0.3650971076346237</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4806020536495886</v>
+        <v>0.4823540064522583</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8359065145344586</v>
+        <v>0.7569069661511347</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6751892205429838</v>
+        <v>0.6747926694080816</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6531518410826856</v>
+        <v>0.6550208228687093</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.967366362348528</v>
+        <v>6.803004516331647</v>
       </c>
       <c r="E10" t="n">
-        <v>615.1583541905333</v>
+        <v>799.3177039369992</v>
       </c>
       <c r="F10" t="n">
-        <v>1.079021978156511</v>
+        <v>1.002082037603418</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8190478404621017</v>
+        <v>0.8195246397726602</v>
       </c>
       <c r="H10" t="n">
-        <v>1.317410198588319</v>
+        <v>1.222760108691058</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6637410905258215</v>
+        <v>0.6638978083415198</v>
       </c>
       <c r="N10" t="n">
-        <v>1.094236020897001</v>
+        <v>1.094919298921563</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.631790595127649</v>
+        <v>6.452790611061825</v>
       </c>
       <c r="E11" t="n">
-        <v>191.578129734891</v>
+        <v>224.3687673340698</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2728922349286476</v>
+        <v>-0.3011252050043328</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9550756106235556</v>
+        <v>0.9560377490778937</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2857284092413165</v>
+        <v>-0.3149720869231059</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7132160030266401</v>
+        <v>0.7133124649948803</v>
       </c>
       <c r="N11" t="n">
-        <v>1.371077067843366</v>
+        <v>1.372377894697278</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.422544823738298</v>
+        <v>6.233533933251069</v>
       </c>
       <c r="E12" t="n">
-        <v>81.45964055500613</v>
+        <v>93.29524227014252</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2666435669002752</v>
+        <v>-0.2868010791821699</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6559902445614365</v>
+        <v>0.6563591851524356</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4064748967090818</v>
+        <v>-0.4369575160520714</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.788815289120564</v>
+        <v>0.7888803953854783</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041539472445167</v>
+        <v>1.042009289648543</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.957153530657654</v>
+        <v>4.835704884631444</v>
       </c>
       <c r="E13" t="n">
-        <v>274.6923098876744</v>
+        <v>363.2771962817695</v>
       </c>
       <c r="F13" t="n">
-        <v>1.902131122351304</v>
+        <v>1.804582404708308</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8597472677947414</v>
+        <v>0.8583125308326802</v>
       </c>
       <c r="H13" t="n">
-        <v>2.212430552097346</v>
+        <v>2.102477058045066</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6022813765851497</v>
+        <v>0.602412211165703</v>
       </c>
       <c r="N13" t="n">
-        <v>1.04225328279176</v>
+        <v>1.040538322672344</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.619745174064216</v>
+        <v>4.521977189199465</v>
       </c>
       <c r="E14" t="n">
-        <v>65.40939641184102</v>
+        <v>87.71703602726308</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3893444486799922</v>
+        <v>-0.4052503292438178</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8472139448521336</v>
+        <v>0.8472248103896703</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4595585932523165</v>
+        <v>-0.478326796234199</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601643860200781</v>
+        <v>0.760247399701551</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296294407459475</v>
+        <v>1.296201348149467</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.336674885575214</v>
+        <v>4.219771178351581</v>
       </c>
       <c r="E15" t="n">
-        <v>181.9153836236416</v>
+        <v>192.7094884625479</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6124940314801188</v>
+        <v>0.5474697291446602</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9572395918967149</v>
+        <v>0.9578156845173483</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6398544697325956</v>
+        <v>0.5715815036173008</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5137943586169349</v>
+        <v>0.514071098217847</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9899494470743128</v>
+        <v>0.9908866847372114</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.188881538934218</v>
+        <v>4.022640258632285</v>
       </c>
       <c r="E16" t="n">
-        <v>143.3375841124926</v>
+        <v>185.4694824622929</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0100637633150793</v>
+        <v>-0.06503011290195293</v>
       </c>
       <c r="G16" t="n">
-        <v>0.791446817227701</v>
+        <v>0.7933291761621547</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.01271565327703369</v>
+        <v>-0.08197116008835773</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7135697525723229</v>
+        <v>0.7131444850539216</v>
       </c>
       <c r="N16" t="n">
-        <v>1.13674015720532</v>
+        <v>1.138543988944966</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.696089224083612</v>
+        <v>3.644444561207028</v>
       </c>
       <c r="E17" t="n">
-        <v>117.3003168007247</v>
+        <v>116.7716156383846</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1066449996268219</v>
+        <v>-0.1266331147914725</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7533538759261401</v>
+        <v>0.753261151039869</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1415602985990047</v>
+        <v>-0.1681131631661302</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7215253259508052</v>
+        <v>0.7215888667493832</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094091489104776</v>
+        <v>1.093841140535515</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.148477279284114</v>
+        <v>3.096186894885869</v>
       </c>
       <c r="E18" t="n">
-        <v>47.50800245950783</v>
+        <v>55.48826731980619</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4566907788119633</v>
+        <v>-0.4695675248378141</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7431942192558151</v>
+        <v>0.7434071854077828</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6144972161775731</v>
+        <v>-0.6316424350677228</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7644426590128305</v>
+        <v>0.7645467493891688</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143537129837744</v>
+        <v>1.143798863675227</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.978905779867103</v>
+        <v>2.918825158126105</v>
       </c>
       <c r="E19" t="n">
-        <v>44.78159655801142</v>
+        <v>53.29893721425265</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1201566636542351</v>
+        <v>0.08887666669685412</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4794953644627805</v>
+        <v>0.4802373414133096</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2505898337283339</v>
+        <v>0.1850682132199371</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7177248181571625</v>
+        <v>0.717603392818757</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6927003545031745</v>
+        <v>0.6935204466092374</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.712656250474298</v>
+        <v>2.634154662250694</v>
       </c>
       <c r="E20" t="n">
-        <v>133.1995201665432</v>
+        <v>165.0932161142688</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2761459706685456</v>
+        <v>-0.3040362726022393</v>
       </c>
       <c r="G20" t="n">
-        <v>0.776026210266585</v>
+        <v>0.7755442654694297</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3558461905219443</v>
+        <v>-0.3920295541328115</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7321729202989959</v>
+        <v>0.7325426790217112</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143649870347099</v>
+        <v>1.143295208711476</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-30.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-30.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>567.4935324880297</v>
+        <v>567.7586441351768</v>
       </c>
       <c r="E2" t="n">
-        <v>7889.367504535481</v>
+        <v>8244.919095737192</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6048006168441964</v>
+        <v>0.6088740069380938</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4969138938027969</v>
+        <v>0.4968756639456445</v>
       </c>
       <c r="H2" t="n">
-        <v>1.217113516822323</v>
+        <v>1.225405168977447</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>224.9495154108557</v>
+        <v>225.0434649335863</v>
       </c>
       <c r="E3" t="n">
-        <v>3606.930637494635</v>
+        <v>3833.161106959702</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2478961079873427</v>
+        <v>0.2510478569102512</v>
       </c>
       <c r="G3" t="n">
-        <v>0.595876977718001</v>
+        <v>0.5958199549155261</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4160189389036266</v>
+        <v>0.4213485212086329</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907295078499181</v>
+        <v>0.8907037543009229</v>
       </c>
       <c r="N3" t="n">
-        <v>1.068123096820651</v>
+        <v>1.068072174266762</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.17781422738018</v>
+        <v>37.23959105567988</v>
       </c>
       <c r="E4" t="n">
-        <v>445.424252837517</v>
+        <v>450.8563827248706</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3306013608702448</v>
+        <v>-0.3291131154556072</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5594014265704497</v>
+        <v>0.5593926842136278</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5909912723982117</v>
+        <v>-0.5883400422339478</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.736208017526488</v>
+        <v>0.7361960878223285</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8287870804038321</v>
+        <v>0.8288244636580854</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.89474913854026</v>
+        <v>37.14346995576943</v>
       </c>
       <c r="E5" t="n">
-        <v>1246.25039644709</v>
+        <v>1281.833662172947</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7325267588529449</v>
+        <v>0.7528457795777583</v>
       </c>
       <c r="G5" t="n">
-        <v>1.104723151079294</v>
+        <v>1.104547985633999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6630862747261881</v>
+        <v>0.6815872097631254</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4738148328705722</v>
+        <v>0.4736912538373309</v>
       </c>
       <c r="N5" t="n">
-        <v>1.053370054097573</v>
+        <v>1.053009350636469</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.89403411519803</v>
+        <v>10.96344114423798</v>
       </c>
       <c r="E6" t="n">
-        <v>458.6166819497926</v>
+        <v>452.9282077766169</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.484000124591757</v>
+        <v>-0.4792580691047181</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8134532072756746</v>
+        <v>0.8131285314745492</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5949944265543133</v>
+        <v>-0.5894001385434338</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6668151763635847</v>
+        <v>0.6667815699810538</v>
       </c>
       <c r="N6" t="n">
-        <v>1.091583372165312</v>
+        <v>1.091176642678761</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.8145519491741</v>
+        <v>10.88239603360462</v>
       </c>
       <c r="E7" t="n">
-        <v>176.5028974099286</v>
+        <v>179.9860538181164</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3055980018791926</v>
+        <v>-0.2995601000912977</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7120044138093254</v>
+        <v>0.7118936780832429</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4292080160629899</v>
+        <v>-0.4207933141053539</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.750917551930409</v>
+        <v>0.7508439028512958</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075954240863964</v>
+        <v>1.075764152791471</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.74182892171579</v>
+        <v>9.805002752049345</v>
       </c>
       <c r="E8" t="n">
-        <v>338.1055048091164</v>
+        <v>351.5093254556934</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3336723127099466</v>
+        <v>-0.3262290764984134</v>
       </c>
       <c r="G8" t="n">
-        <v>1.168488284969429</v>
+        <v>1.168117927459841</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2855589713667318</v>
+        <v>-0.2792775188441999</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7374441989286451</v>
+        <v>0.7374200968027091</v>
       </c>
       <c r="N8" t="n">
-        <v>1.734093004871293</v>
+        <v>1.73362009381616</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.154286794179395</v>
+        <v>7.161205425101189</v>
       </c>
       <c r="E9" t="n">
-        <v>224.6768150091932</v>
+        <v>228.7231631573492</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3650971076346237</v>
+        <v>0.3678538441528962</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4823540064522583</v>
+        <v>0.4821870501637102</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7569069661511347</v>
+        <v>0.7628861953634052</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6747926694080816</v>
+        <v>0.6745797103938891</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6550208228687093</v>
+        <v>0.6546378183873027</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.803004516331647</v>
+        <v>6.86543302446687</v>
       </c>
       <c r="E10" t="n">
-        <v>799.3177039369992</v>
+        <v>815.390264485885</v>
       </c>
       <c r="F10" t="n">
-        <v>1.002082037603418</v>
+        <v>1.033003069329685</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8195246397726602</v>
+        <v>0.8191813971950231</v>
       </c>
       <c r="H10" t="n">
-        <v>1.222760108691058</v>
+        <v>1.261018710711465</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6638978083415198</v>
+        <v>0.66383232843889</v>
       </c>
       <c r="N10" t="n">
-        <v>1.094919298921563</v>
+        <v>1.094436966374115</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.452790611061825</v>
+        <v>6.470708567999787</v>
       </c>
       <c r="E11" t="n">
-        <v>224.3687673340698</v>
+        <v>228.6750199418295</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3011252050043328</v>
+        <v>-0.296507501124768</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9560377490778937</v>
+        <v>0.9558008990002678</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3149720869231059</v>
+        <v>-0.3102188975077381</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7133124649948803</v>
+        <v>0.7132541408348129</v>
       </c>
       <c r="N11" t="n">
-        <v>1.372377894697278</v>
+        <v>1.37203127159022</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.233533933251069</v>
+        <v>6.260903135653495</v>
       </c>
       <c r="E12" t="n">
-        <v>93.29524227014252</v>
+        <v>95.49149424312635</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2868010791821699</v>
+        <v>-0.2827065446863161</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6563591851524356</v>
+        <v>0.656214773745858</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4369575160520714</v>
+        <v>-0.4308140505166438</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7888803953854783</v>
+        <v>0.7888544463013379</v>
       </c>
       <c r="N12" t="n">
-        <v>1.042009289648543</v>
+        <v>1.041825912517776</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.835704884631444</v>
+        <v>4.900508176434337</v>
       </c>
       <c r="E13" t="n">
-        <v>363.2771962817695</v>
+        <v>376.5196459564082</v>
       </c>
       <c r="F13" t="n">
-        <v>1.804582404708308</v>
+        <v>1.865450839466044</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8583125308326802</v>
+        <v>0.8590830499737681</v>
       </c>
       <c r="H13" t="n">
-        <v>2.102477058045066</v>
+        <v>2.171444122338353</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.602412211165703</v>
+        <v>0.6017021237434336</v>
       </c>
       <c r="N13" t="n">
-        <v>1.040538322672344</v>
+        <v>1.040324840094704</v>
       </c>
     </row>
     <row r="14">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.521977189199465</v>
+        <v>4.529802420627514</v>
       </c>
       <c r="E14" t="n">
-        <v>87.71703602726308</v>
+        <v>91.20330492164035</v>
       </c>
       <c r="F14" t="n">
         <v>-0.4052503292438178</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.760247399701551</v>
+        <v>0.760245790516063</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296201348149467</v>
+        <v>1.296298334687564</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.219771178351581</v>
+        <v>4.241944412501832</v>
       </c>
       <c r="E15" t="n">
-        <v>192.7094884625479</v>
+        <v>195.1078312238965</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5474697291446602</v>
+        <v>0.5636617673917759</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9578156845173483</v>
+        <v>0.9575525598082728</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5715815036173008</v>
+        <v>0.5886483844862112</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.514071098217847</v>
+        <v>0.5139595482163981</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9908866847372114</v>
+        <v>0.9904757200713963</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.022640258632285</v>
+        <v>4.048057334344136</v>
       </c>
       <c r="E16" t="n">
-        <v>185.4694824622929</v>
+        <v>192.177922233734</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.06503011290195293</v>
+        <v>-0.05696252336299545</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7933291761621547</v>
+        <v>0.7928710131859152</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.08197116008835773</v>
+        <v>-0.0718433672257844</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7131444850539216</v>
+        <v>0.7131713372394693</v>
       </c>
       <c r="N16" t="n">
-        <v>1.138543988944966</v>
+        <v>1.138016855649565</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.644444561207028</v>
+        <v>3.659588234312021</v>
       </c>
       <c r="E17" t="n">
-        <v>116.7716156383846</v>
+        <v>116.6628471894842</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1266331147914725</v>
+        <v>-0.1167468637575646</v>
       </c>
       <c r="G17" t="n">
-        <v>0.753261151039869</v>
+        <v>0.7532441928682135</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1681131631661302</v>
+        <v>-0.1549920528600616</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7215888667493832</v>
+        <v>0.7214264294568548</v>
       </c>
       <c r="N17" t="n">
-        <v>1.093841140535515</v>
+        <v>1.093654425042382</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.096186894885869</v>
+        <v>3.112115909876264</v>
       </c>
       <c r="E18" t="n">
-        <v>55.48826731980619</v>
+        <v>56.63366326596325</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4695675248378141</v>
+        <v>-0.4655769664140613</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7434071854077828</v>
+        <v>0.7432810823800423</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6316424350677228</v>
+        <v>-0.626380756151157</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645467493891688</v>
+        <v>0.7644978877419717</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143798863675227</v>
+        <v>1.14361973972682</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.918825158126105</v>
+        <v>2.91835061621758</v>
       </c>
       <c r="E19" t="n">
-        <v>53.29893721425265</v>
+        <v>53.24066646546332</v>
       </c>
       <c r="F19" t="n">
-        <v>0.08887666669685412</v>
+        <v>0.08796009224442081</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4802373414133096</v>
+        <v>0.4802772761631743</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1850682132199371</v>
+        <v>0.1831443972263563</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.717603392818757</v>
+        <v>0.7173787746687774</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6935204466092374</v>
+        <v>0.6934143667637684</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.634154662250694</v>
+        <v>2.655951249774479</v>
       </c>
       <c r="E20" t="n">
-        <v>165.0932161142688</v>
+        <v>169.1568995050384</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3040362726022393</v>
+        <v>-0.2959515668345636</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7755442654694297</v>
+        <v>0.7755307703377796</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3920295541328115</v>
+        <v>-0.3816116370284869</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7325426790217112</v>
+        <v>0.7323801548720656</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143295208711476</v>
+        <v>1.143109608503929</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-30.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-30.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>567.7586441351768</v>
+        <v>570.2615835949629</v>
       </c>
       <c r="E2" t="n">
-        <v>8244.919095737192</v>
+        <v>6613.889114995178</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6088740069380938</v>
+        <v>0.6195465762411225</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4968756639456445</v>
+        <v>0.4968200646910677</v>
       </c>
       <c r="H2" t="n">
-        <v>1.225405168977447</v>
+        <v>1.247024064187844</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>225.0434649335863</v>
+        <v>226.8054736708407</v>
       </c>
       <c r="E3" t="n">
-        <v>3833.161106959702</v>
+        <v>2826.495503631028</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2510478569102512</v>
+        <v>0.2673897680540887</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5958199549155261</v>
+        <v>0.5956470783545122</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4213485212086329</v>
+        <v>0.4489063705185268</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,45 +598,45 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907037543009229</v>
+        <v>0.8907014668728902</v>
       </c>
       <c r="N3" t="n">
-        <v>1.068072174266762</v>
+        <v>1.067879025294233</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.23959105567988</v>
+        <v>37.75044247103453</v>
       </c>
       <c r="E4" t="n">
-        <v>450.8563827248706</v>
+        <v>1063.175638598855</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3291131154556072</v>
+        <v>0.785615338699112</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5593926842136278</v>
+        <v>1.104450648428243</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5883400422339478</v>
+        <v>0.7113177395632214</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3496897913141569</v>
+        <v>0.3422195892575038</v>
       </c>
       <c r="J4" t="n">
         <v>272</v>
@@ -652,45 +652,45 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7361960878223285</v>
+        <v>0.4735750688693525</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8288244636580854</v>
+        <v>1.052776103592842</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.14346995576943</v>
+        <v>37.40147238525294</v>
       </c>
       <c r="E5" t="n">
-        <v>1281.833662172947</v>
+        <v>406.7038488625988</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7528457795777583</v>
+        <v>-0.3250161035158924</v>
       </c>
       <c r="G5" t="n">
-        <v>1.104547985633999</v>
+        <v>0.5594018629207999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6815872097631254</v>
+        <v>-0.5810064732693037</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3422195892575038</v>
+        <v>0.3496897913141569</v>
       </c>
       <c r="J5" t="n">
         <v>272</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4736912538373309</v>
+        <v>0.736194618365602</v>
       </c>
       <c r="N5" t="n">
-        <v>1.053009350636469</v>
+        <v>0.8289291642077057</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.96344114423798</v>
+        <v>11.13501845457639</v>
       </c>
       <c r="E6" t="n">
-        <v>452.9282077766169</v>
+        <v>532.3567766836671</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4792580691047181</v>
+        <v>-0.4681204491106474</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8131285314745492</v>
+        <v>0.812646119638597</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5894001385434338</v>
+        <v>-0.5760446494457289</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6667815699810538</v>
+        <v>0.6667280353589129</v>
       </c>
       <c r="N6" t="n">
-        <v>1.091176642678761</v>
+        <v>1.090563745901841</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.88239603360462</v>
+        <v>11.01963530703672</v>
       </c>
       <c r="E7" t="n">
-        <v>179.9860538181164</v>
+        <v>161.884326521974</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2995601000912977</v>
+        <v>-0.2907815497200198</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7118936780832429</v>
+        <v>0.7118679306033032</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4207933141053539</v>
+        <v>-0.4084768216396325</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7508439028512958</v>
+        <v>0.750780342200046</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075764152791471</v>
+        <v>1.075754556877492</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.805002752049345</v>
+        <v>10.08434826264828</v>
       </c>
       <c r="E8" t="n">
-        <v>351.5093254556934</v>
+        <v>264.4174221139738</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3262290764984134</v>
+        <v>-0.3026460824286126</v>
       </c>
       <c r="G8" t="n">
-        <v>1.168117927459841</v>
+        <v>1.167418501174469</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2792775188441999</v>
+        <v>-0.2592438633824448</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7374200968027091</v>
+        <v>0.7374254028575749</v>
       </c>
       <c r="N8" t="n">
-        <v>1.73362009381616</v>
+        <v>1.732788427269506</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.161205425101189</v>
+        <v>7.277967874967039</v>
       </c>
       <c r="E9" t="n">
-        <v>228.7231631573492</v>
+        <v>199.7459228351568</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3678538441528962</v>
+        <v>0.4065962383606763</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4821870501637102</v>
+        <v>0.4804453707602968</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7628861953634052</v>
+        <v>0.8462902612991036</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6745797103938891</v>
+        <v>0.6757705653476709</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6546378183873027</v>
+        <v>0.6534978413547845</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.86543302446687</v>
+        <v>6.947888917884047</v>
       </c>
       <c r="E10" t="n">
-        <v>815.390264485885</v>
+        <v>617.7675334519056</v>
       </c>
       <c r="F10" t="n">
-        <v>1.033003069329685</v>
+        <v>1.069621055884787</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8191813971950231</v>
+        <v>0.8190387359462802</v>
       </c>
       <c r="H10" t="n">
-        <v>1.261018710711465</v>
+        <v>1.305946848348992</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.66383232843889</v>
+        <v>0.6637326940577906</v>
       </c>
       <c r="N10" t="n">
-        <v>1.094436966374115</v>
+        <v>1.094204573008433</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.470708567999787</v>
+        <v>6.609691052032476</v>
       </c>
       <c r="E11" t="n">
-        <v>228.6750199418295</v>
+        <v>194.0926457947774</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.296507501124768</v>
+        <v>-0.2780964033804886</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9558008990002678</v>
+        <v>0.9551661246454288</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3102188975077381</v>
+        <v>-0.2911497761540924</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7132541408348129</v>
+        <v>0.7132511673023336</v>
       </c>
       <c r="N11" t="n">
-        <v>1.37203127159022</v>
+        <v>1.371267792484643</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.260903135653495</v>
+        <v>6.416604985788151</v>
       </c>
       <c r="E12" t="n">
-        <v>95.49149424312635</v>
+        <v>82.46109773679497</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2827065446863161</v>
+        <v>-0.2675799387003731</v>
       </c>
       <c r="G12" t="n">
-        <v>0.656214773745858</v>
+        <v>0.65598846629226</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4308140505166438</v>
+        <v>-0.4079034197243938</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7888544463013379</v>
+        <v>0.7888036324989671</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041825912517776</v>
+        <v>1.04151607767798</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.900508176434337</v>
+        <v>4.931784496446302</v>
       </c>
       <c r="E13" t="n">
-        <v>376.5196459564082</v>
+        <v>303.637401006557</v>
       </c>
       <c r="F13" t="n">
-        <v>1.865450839466044</v>
+        <v>1.883776121363141</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8590830499737681</v>
+        <v>0.8593962579487361</v>
       </c>
       <c r="H13" t="n">
-        <v>2.171444122338353</v>
+        <v>2.191976173900807</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6017021237434336</v>
+        <v>0.6021089654634717</v>
       </c>
       <c r="N13" t="n">
-        <v>1.040324840094704</v>
+        <v>1.041524343664447</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.529802420627514</v>
+        <v>4.602384805113891</v>
       </c>
       <c r="E14" t="n">
-        <v>91.20330492164035</v>
+        <v>67.22184495341749</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4052503292438178</v>
+        <v>-0.3936373125792902</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8472248103896703</v>
+        <v>0.8471575153583234</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.478326796234199</v>
+        <v>-0.4646565785499677</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.760245790516063</v>
+        <v>0.760153111087419</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296298334687564</v>
+        <v>1.296182394084969</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.241944412501832</v>
+        <v>4.326684438503555</v>
       </c>
       <c r="E15" t="n">
-        <v>195.1078312238965</v>
+        <v>183.0252116455603</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5636617673917759</v>
+        <v>0.602968949821461</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9575525598082728</v>
+        <v>0.9572444529480665</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5886483844862112</v>
+        <v>0.6299006987864718</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5139595482163981</v>
+        <v>0.513799591993835</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9904757200713963</v>
+        <v>0.989959633914763</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.048057334344136</v>
+        <v>4.172509046072678</v>
       </c>
       <c r="E16" t="n">
-        <v>192.177922233734</v>
+        <v>144.8042520224251</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.05696252336299545</v>
+        <v>-0.02315869806192372</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7928710131859152</v>
+        <v>0.7916336603926114</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0718433672257844</v>
+        <v>-0.02925431196348845</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7131713372394693</v>
+        <v>0.7135211972519842</v>
       </c>
       <c r="N16" t="n">
-        <v>1.138016855649565</v>
+        <v>1.136925493336385</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.659588234312021</v>
+        <v>3.692607238674999</v>
       </c>
       <c r="E17" t="n">
-        <v>116.6628471894842</v>
+        <v>118.1599511806155</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1167468637575646</v>
+        <v>-0.1102026959434957</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7532441928682135</v>
+        <v>0.7533006736727427</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1549920528600616</v>
+        <v>-0.146293106849618</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7214264294568548</v>
+        <v>0.7214708549791402</v>
       </c>
       <c r="N17" t="n">
-        <v>1.093654425042382</v>
+        <v>1.093926191223749</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.112115909876264</v>
+        <v>3.143518321463928</v>
       </c>
       <c r="E18" t="n">
-        <v>56.63366326596325</v>
+        <v>48.02038374064009</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4655769664140613</v>
+        <v>-0.4585351252806213</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7432810823800423</v>
+        <v>0.7431903450179421</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.626380756151157</v>
+        <v>-0.6169820805052996</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7644978877419717</v>
+        <v>0.764436613715902</v>
       </c>
       <c r="N18" t="n">
-        <v>1.14361973972682</v>
+        <v>1.143516437978683</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.91835061621758</v>
+        <v>2.974525209436718</v>
       </c>
       <c r="E19" t="n">
-        <v>53.24066646546332</v>
+        <v>44.43757104560514</v>
       </c>
       <c r="F19" t="n">
-        <v>0.08796009224442081</v>
+        <v>0.1155425308376925</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4802772761631743</v>
+        <v>0.479529333982196</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1831443972263563</v>
+        <v>0.2409498703200968</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7173787746687774</v>
+        <v>0.7177415808504168</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6934143667637684</v>
+        <v>0.6927621621935612</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.655951249774479</v>
+        <v>2.688908047755418</v>
       </c>
       <c r="E20" t="n">
-        <v>169.1568995050384</v>
+        <v>141.8635252264938</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2959515668345636</v>
+        <v>-0.2863201756665339</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7755307703377796</v>
+        <v>0.7756785757479153</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3816116370284869</v>
+        <v>-0.3691221913541466</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7323801548720656</v>
+        <v>0.732316813152378</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143109608503929</v>
+        <v>1.143356524812476</v>
       </c>
     </row>
   </sheetData>
